--- a/docs/reference/Inventory_Table_synthetic.xlsx
+++ b/docs/reference/Inventory_Table_synthetic.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>43.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="4">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="5">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>39.5</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="6">
@@ -603,7 +603,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Floaters A&amp;B</t>
+          <t>Postgame</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -633,16 +633,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Postgame</t>
+          <t>Pregame</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Expanded</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -663,7 +663,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pregame</t>
+          <t>In Game</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="9">
@@ -693,7 +693,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>In Game</t>
+          <t>In Game+</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>52.5</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>In Game+</t>
+          <t>In Game-</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>56.5</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="11">
@@ -753,7 +753,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>In Game-</t>
+          <t>Postgame</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>48.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -778,21 +778,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Floaters A&amp;B</t>
+          <t>Pregame</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Expanded</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -808,21 +808,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Postgame</t>
+          <t>In Game</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Expanded</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -843,7 +843,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Pregame</t>
+          <t>In Game+</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
@@ -873,7 +873,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>In Game</t>
+          <t>In Game-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -903,7 +903,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>In Game+</t>
+          <t>Postgame</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -933,16 +933,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>In Game-</t>
+          <t>Pregame</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Expanded</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -963,16 +963,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Floaters A&amp;B</t>
+          <t>In Game</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Expanded</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -993,16 +993,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Postgame</t>
+          <t>In Game+</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Expanded</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pregame</t>
+          <t>In Game-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>In Game</t>
+          <t>Postgame</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1083,16 +1083,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>In Game+</t>
+          <t>Pregame</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Expanded</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -1113,16 +1113,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>In Game-</t>
+          <t>In Game</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Expanded</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>54</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="24">
@@ -1143,16 +1143,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Floaters A&amp;B</t>
+          <t>In Game+</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Expanded</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="25">
@@ -1173,16 +1173,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Postgame</t>
+          <t>In Game-</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Expanded</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>17</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pregame</t>
+          <t>Postgame</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
@@ -1233,16 +1233,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>In Game</t>
+          <t>Pregame</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>Expanded DH</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>102.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28">
@@ -1263,16 +1263,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>In Game+</t>
+          <t>In Game</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>Expanded DH</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>106.5</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29">
@@ -1293,16 +1293,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>In Game-</t>
+          <t>In Game</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>Expanded DH</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30">
@@ -1323,16 +1323,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Floaters A&amp;B</t>
+          <t>In Game</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>Expanded DH</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>12</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31">
@@ -1358,190 +1358,10 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>Expanded DH</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>REG</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Pregame</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Expanded DH</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>REG</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>In Game</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Expanded DH</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>REG</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>In Game</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Expanded DH</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>REG</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>In Game</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Expanded DH</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>REG</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Floaters A&amp;B</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Expanded DH</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Sentinels</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>REG</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Postgame</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Expanded DH</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
         <v>42</v>
       </c>
     </row>
